--- a/Take/TS_SVNログからリスト作成_単体テスト.xlsx
+++ b/Take/TS_SVNログからリスト作成_単体テスト.xlsx
@@ -2908,11 +2908,15 @@
       <c r="C9" s="8">
         <v>1</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>14</v>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">他社展開対象ファイルを含むログで一覧作成を実行する。次に、前回とは異なる対象ファイルを含むログに入れ替え、同じ入力シートから再実行する。両方とも正常終了するデータを使用し、各回の対象ファイル名と件数を記録する。</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">リスト・リストedit・UPDATEは今回の入力に対応する内容に更新される。前回のみに含まれる行は残らず、各シートの行と件数は今回の入力と抽出条件に一致する。各正常終了時のメッセージボックスは 実行しました。</t>
+        </is>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="26"/>
@@ -3317,8 +3321,13 @@
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="28" t="s">
-        <v>30</v>
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- 案件が採用された場合、台帳の 本実施環境 に含まれる会社は －、含まれない有効な会社は ○、ログ種別ごとの無効会社列は空欄となる。無効会社はPRが 90/91/92/93、AP・BATCHが 08/0H/52/09/44/44 rch/0F/0X。同期AB列はPRが [ap][wb]、APが [ap][wb][cw]、BATCHが [ap][cw]。
+- 「黄」は黄色背景を示す。
+- SVNのサイズ・日時（F・G列）は実際の取得結果を記録し、照合結果とは分けて判定する。
+- 証跡には入力ログ、UPDATEの照合結果、実行時の台帳を残す。正常終了したケース（TC-4-1-14・TC-4-1-22・TC-4-1-27）は、台帳の画面・ファイルの添付を省略してよい。</t>
+        </is>
       </c>
       <c r="E32" s="28" t="s">
         <v>115</v>
@@ -3677,8 +3686,10 @@
       <c r="C52" s="8">
         <v>1</v>
       </c>
-      <c r="D52" s="28" t="s">
-        <v>58</v>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会社目印 (44) の案件名を持つPRのログを使用する。台帳には、同じ案件名で会社目印 (91) の案件を1行だけ用意し、本実施環境 を 44 として実行する。</t>
+        </is>
       </c>
       <c r="E52" s="28" t="s">
         <v>56</v>
@@ -3713,8 +3724,10 @@
       <c r="C54" s="8">
         <v>1</v>
       </c>
-      <c r="D54" s="28" t="s">
-        <v>117</v>
+      <c r="D54" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会社コード対応 92/0F を保持し、2回に分けて確認する。一方は会社目印 (92) のPRログと、同じ案件名で会社目印 (0F) の台帳1行を使用する。もう一方は会社目印 (0F) のPRログと、同じ案件名で会社目印 (92) の台帳1行を使用する。両方とも 本実施環境 は 0F とする。各回で、会社目印なしの候補やログと同じ目印の候補は用意しない。各方向の結果を別々に記録する。</t>
+        </is>
       </c>
       <c r="E54" s="28" t="s">
         <v>143</v>
@@ -4448,11 +4461,15 @@
       <c r="C95" s="8">
         <v>1</v>
       </c>
-      <c r="D95" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="E95" s="28" t="s">
-        <v>84</v>
+      <c r="D95" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常処理でファイルの重複がないUPDATEを作成し、任意の会社列に ○ が付いた対象行を用意する。その会社コードに対応するシートを持つテスト用棚卸しファイルのフルパスを ※ 棚卸しファイル に入力する。対象会社・ファイル名・件数とUPDATEの同期値を記録し、既存の出力ファイルを閉じて下側の「リストにする」を押す。</t>
+        </is>
+      </c>
+      <c r="E95" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">棚卸しファイル フォルダのコピー内の対象会社シートに、UPDATEでその会社が ○ の対象ファイルが3行目から表示される。ファイル名・件数・モジュール情報がUPDATEの対象行と一致し、Kは対象会社コード、LはUPDATEの同期値となる。メッセージボックスに「棚卸しファイルへ反映しました。」と表示される。元ファイルは変更されない。</t>
+        </is>
       </c>
       <c r="F95" s="25"/>
       <c r="G95" s="26"/>
